--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -74,28 +74,19 @@
     <t>超级明星</t>
   </si>
   <si>
-    <t>500_10000001_1|500_10000002_1</t>
+    <t>500_10000001_1</t>
   </si>
   <si>
     <t>神马飞扬</t>
   </si>
   <si>
-    <t>500_10000003_1|500_20000001_1</t>
-  </si>
-  <si>
     <t>金蛇招财</t>
   </si>
   <si>
     <t>圣诞狂欢夜</t>
   </si>
   <si>
-    <t>500_20000002_1|500_20000003_1</t>
-  </si>
-  <si>
     <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>500_20000002_2|500_20000003_3</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -1252,10 +1243,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.25"/>
+    <col min="1" max="1" width="10.375"/>
     <col min="2" max="4" width="13.625" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="21.375" customWidth="1"/>
@@ -1338,7 +1329,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:7">
       <c r="A5" s="1">
-        <v>1003001</v>
+        <v>10030001</v>
       </c>
       <c r="B5" s="1">
         <v>100300</v>
@@ -1350,7 +1341,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>15</v>
@@ -1361,19 +1352,19 @@
     </row>
     <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="1">
-        <v>1003002</v>
+        <v>10340001</v>
       </c>
       <c r="B6" s="1">
-        <v>100300</v>
+        <v>103400</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1">
         <v>1001</v>
       </c>
       <c r="E6" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>15</v>
@@ -1384,22 +1375,22 @@
     </row>
     <row r="7" ht="16.5" spans="1:7">
       <c r="A7" s="1">
-        <v>1034001</v>
+        <v>10350001</v>
       </c>
       <c r="B7" s="1">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1">
         <v>1001</v>
       </c>
       <c r="E7" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
         <v>99999</v>
@@ -1407,10 +1398,10 @@
     </row>
     <row r="8" ht="16.5" spans="1:7">
       <c r="A8" s="1">
-        <v>1035001</v>
+        <v>10170001</v>
       </c>
       <c r="B8" s="1">
-        <v>103500</v>
+        <v>101700</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -1419,10 +1410,10 @@
         <v>1001</v>
       </c>
       <c r="E8" s="1">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>99999</v>
@@ -1430,10 +1421,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:7">
       <c r="A9" s="1">
-        <v>1017001</v>
+        <v>10180001</v>
       </c>
       <c r="B9" s="1">
-        <v>101700</v>
+        <v>101800</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
@@ -1442,10 +1433,10 @@
         <v>1001</v>
       </c>
       <c r="E9" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1">
         <v>99999</v>
@@ -1453,47 +1444,24 @@
     </row>
     <row r="10" ht="16.5" spans="1:7">
       <c r="A10" s="1">
-        <v>1018001</v>
+        <v>10210001</v>
       </c>
       <c r="B10" s="1">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1">
         <v>1001</v>
       </c>
       <c r="E10" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:7">
-      <c r="A11" s="1">
-        <v>1021001</v>
-      </c>
-      <c r="B11" s="1">
-        <v>102100</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1001</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6000</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="1">
         <v>99999</v>
       </c>
     </row>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>id</t>
   </si>
@@ -77,19 +77,61 @@
     <t>500_10000001_1</t>
   </si>
   <si>
+    <t>500_10000002_1</t>
+  </si>
+  <si>
     <t>神马飞扬</t>
   </si>
   <si>
+    <t>500_10000003_1</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>500_10000004_1</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>500_10000005_1</t>
+  </si>
+  <si>
     <t>金蛇招财</t>
   </si>
   <si>
+    <t>500_10000006_1</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>500_10000007_1</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>500_10000008_1</t>
+  </si>
+  <si>
+    <t>牛气冲天</t>
+  </si>
+  <si>
+    <t>500_10000009_1</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>500_10000010_1</t>
+  </si>
+  <si>
     <t>圣诞狂欢夜</t>
   </si>
   <si>
-    <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>杰克船长</t>
+    <t>500_10000011_1</t>
   </si>
 </sst>
 </file>
@@ -711,8 +753,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1243,225 +1288,548 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10.375"/>
-    <col min="2" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
-    <col min="7" max="7" width="16.25" customWidth="1"/>
+    <col min="1" max="1" width="10.375" style="1"/>
+    <col min="2" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:7">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:7">
-      <c r="A5" s="1">
+    <row r="4" spans="1:7">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
         <v>10030001</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>100300</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>1001</v>
       </c>
-      <c r="E5" s="1">
-        <v>10000</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:7">
-      <c r="A6" s="1">
+      <c r="G5" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>10030002</v>
+      </c>
+      <c r="B6" s="2">
+        <v>100300</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="E6" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
         <v>10340001</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="2">
         <v>103400</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2">
         <v>1001</v>
       </c>
-      <c r="E6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E7" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:7">
-      <c r="A7" s="1">
+      <c r="G7" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>10340002</v>
+      </c>
+      <c r="B8" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1003</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>10340101</v>
+      </c>
+      <c r="B9" s="2">
+        <v>103401</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>10340102</v>
+      </c>
+      <c r="B10" s="2">
+        <v>103401</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1003</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>10140001</v>
+      </c>
+      <c r="B11" s="2">
+        <v>101400</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>10140002</v>
+      </c>
+      <c r="B12" s="2">
+        <v>101400</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1004</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
         <v>10350001</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B13" s="2">
         <v>103500</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="2">
         <v>1001</v>
       </c>
-      <c r="E7" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E13" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:7">
-      <c r="A8" s="1">
+      <c r="G13" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>10350002</v>
+      </c>
+      <c r="B14" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1004</v>
+      </c>
+      <c r="E14" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>10350101</v>
+      </c>
+      <c r="B15" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>10350102</v>
+      </c>
+      <c r="B16" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1004</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>10070001</v>
+      </c>
+      <c r="B17" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
+        <v>10070002</v>
+      </c>
+      <c r="B18" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
+        <v>10370001</v>
+      </c>
+      <c r="B19" s="1">
+        <v>103700</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E19" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
+        <v>10370002</v>
+      </c>
+      <c r="B20" s="1">
+        <v>103700</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
+        <v>10360001</v>
+      </c>
+      <c r="B21" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E21" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1">
+        <v>10360002</v>
+      </c>
+      <c r="B22" s="1">
+        <v>103600</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E22" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1">
         <v>10170001</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B23" s="1">
         <v>101700</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="2">
         <v>1001</v>
       </c>
-      <c r="E8" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E23" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:7">
-      <c r="A9" s="1">
-        <v>10180001</v>
-      </c>
-      <c r="B9" s="1">
-        <v>101800</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1001</v>
-      </c>
-      <c r="E9" s="1">
-        <v>5000</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:7">
-      <c r="A10" s="1">
-        <v>10210001</v>
-      </c>
-      <c r="B10" s="1">
-        <v>102100</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1001</v>
-      </c>
-      <c r="E10" s="1">
-        <v>6000</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="G23" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1">
+        <v>10170002</v>
+      </c>
+      <c r="B24" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E24" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="2">
         <v>99999</v>
       </c>
     </row>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -1387,7 +1387,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1410,7 +1410,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -1433,7 +1433,7 @@
         <v>1001</v>
       </c>
       <c r="E7" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
@@ -1456,7 +1456,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1479,7 +1479,7 @@
         <v>1001</v>
       </c>
       <c r="E9" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -1502,7 +1502,7 @@
         <v>1003</v>
       </c>
       <c r="E10" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -1525,7 +1525,7 @@
         <v>1001</v>
       </c>
       <c r="E11" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>15</v>
@@ -1548,7 +1548,7 @@
         <v>1004</v>
       </c>
       <c r="E12" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1571,7 +1571,7 @@
         <v>1001</v>
       </c>
       <c r="E13" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>15</v>
@@ -1594,7 +1594,7 @@
         <v>1004</v>
       </c>
       <c r="E14" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
@@ -1617,7 +1617,7 @@
         <v>1001</v>
       </c>
       <c r="E15" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>15</v>
@@ -1640,7 +1640,7 @@
         <v>1004</v>
       </c>
       <c r="E16" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>26</v>
@@ -1663,7 +1663,7 @@
         <v>1001</v>
       </c>
       <c r="E17" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>15</v>
@@ -1686,7 +1686,7 @@
         <v>1003</v>
       </c>
       <c r="E18" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
@@ -1709,7 +1709,7 @@
         <v>1001</v>
       </c>
       <c r="E19" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
@@ -1732,7 +1732,7 @@
         <v>1003</v>
       </c>
       <c r="E20" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>30</v>
@@ -1755,7 +1755,7 @@
         <v>1001</v>
       </c>
       <c r="E21" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>15</v>
@@ -1778,7 +1778,7 @@
         <v>1003</v>
       </c>
       <c r="E22" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1801,7 +1801,7 @@
         <v>1001</v>
       </c>
       <c r="E23" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>15</v>
@@ -1824,7 +1824,7 @@
         <v>1003</v>
       </c>
       <c r="E24" s="2">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>500_10000011_1</t>
+  </si>
+  <si>
+    <t>财神到</t>
+  </si>
+  <si>
+    <t>500_10000012_1</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1294,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1833,6 +1839,52 @@
         <v>99999</v>
       </c>
     </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="B25" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E25" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="B26" s="1">
+        <v>101200</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="1">
+        <v>99999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -138,6 +138,48 @@
   </si>
   <si>
     <t>500_10000012_1</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>500_10000013_1</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>500_10000014_1</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>500_10000015_1</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>500_10000016_1</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>500_10000017_1</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>500_10000018_1</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>500_10000019_1</t>
   </si>
 </sst>
 </file>
@@ -150,7 +192,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +203,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -503,12 +551,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -629,137 +692,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -767,6 +830,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1294,7 +1360,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1885,6 +1951,328 @@
         <v>99999</v>
       </c>
     </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1">
+        <v>10180001</v>
+      </c>
+      <c r="B27" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E27" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="1">
+        <v>10180002</v>
+      </c>
+      <c r="B28" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3">
+        <v>10250001</v>
+      </c>
+      <c r="B29" s="3">
+        <v>102500</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3">
+        <v>10250002</v>
+      </c>
+      <c r="B30" s="3">
+        <v>102500</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E30" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3">
+        <v>10310001</v>
+      </c>
+      <c r="B31" s="3">
+        <v>103100</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E31" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3">
+        <v>10310002</v>
+      </c>
+      <c r="B32" s="3">
+        <v>103100</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1004</v>
+      </c>
+      <c r="E32" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3">
+        <v>10220001</v>
+      </c>
+      <c r="B33" s="3">
+        <v>102200</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="3">
+        <v>10220002</v>
+      </c>
+      <c r="B34" s="3">
+        <v>102200</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E34" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="3">
+        <v>10210001</v>
+      </c>
+      <c r="B35" s="3">
+        <v>102100</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E35" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="3">
+        <v>10210002</v>
+      </c>
+      <c r="B36" s="3">
+        <v>102100</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E36" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="3">
+        <v>10390001</v>
+      </c>
+      <c r="B37" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E37" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="3">
+        <v>10390002</v>
+      </c>
+      <c r="B38" s="3">
+        <v>103900</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="3">
+        <v>10200001</v>
+      </c>
+      <c r="B39" s="3">
+        <v>102000</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E39" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="3">
+        <v>10200002</v>
+      </c>
+      <c r="B40" s="3">
+        <v>102000</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E40" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" s="1">
+        <v>99999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="dropItem" sheetId="1" r:id="rId1"/>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropItem" sheetId="1" r:id="rId1"/>
@@ -1459,7 +1459,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1482,7 +1482,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -1505,7 +1505,7 @@
         <v>1001</v>
       </c>
       <c r="E7" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
@@ -1528,7 +1528,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1551,7 +1551,7 @@
         <v>1001</v>
       </c>
       <c r="E9" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -1574,7 +1574,7 @@
         <v>1003</v>
       </c>
       <c r="E10" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -1597,7 +1597,7 @@
         <v>1001</v>
       </c>
       <c r="E11" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>15</v>
@@ -1620,7 +1620,7 @@
         <v>1004</v>
       </c>
       <c r="E12" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1643,7 +1643,7 @@
         <v>1001</v>
       </c>
       <c r="E13" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>15</v>
@@ -1666,7 +1666,7 @@
         <v>1004</v>
       </c>
       <c r="E14" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
@@ -1689,7 +1689,7 @@
         <v>1001</v>
       </c>
       <c r="E15" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>15</v>
@@ -1712,7 +1712,7 @@
         <v>1004</v>
       </c>
       <c r="E16" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>26</v>
@@ -1735,7 +1735,7 @@
         <v>1001</v>
       </c>
       <c r="E17" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>15</v>
@@ -1758,7 +1758,7 @@
         <v>1003</v>
       </c>
       <c r="E18" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
@@ -1781,7 +1781,7 @@
         <v>1001</v>
       </c>
       <c r="E19" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
@@ -1804,7 +1804,7 @@
         <v>1003</v>
       </c>
       <c r="E20" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>30</v>
@@ -1827,7 +1827,7 @@
         <v>1001</v>
       </c>
       <c r="E21" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>15</v>
@@ -1850,7 +1850,7 @@
         <v>1003</v>
       </c>
       <c r="E22" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1873,7 +1873,7 @@
         <v>1001</v>
       </c>
       <c r="E23" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>15</v>
@@ -1896,7 +1896,7 @@
         <v>1003</v>
       </c>
       <c r="E24" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -1919,7 +1919,7 @@
         <v>1001</v>
       </c>
       <c r="E25" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>15</v>
@@ -1941,8 +1941,8 @@
       <c r="D26" s="1">
         <v>1003</v>
       </c>
-      <c r="E26" s="1">
-        <v>5000</v>
+      <c r="E26" s="2">
+        <v>2000</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>36</v>
@@ -1965,7 +1965,7 @@
         <v>1001</v>
       </c>
       <c r="E27" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>15</v>
@@ -1987,8 +1987,8 @@
       <c r="D28" s="1">
         <v>1005</v>
       </c>
-      <c r="E28" s="1">
-        <v>5000</v>
+      <c r="E28" s="2">
+        <v>2000</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -2011,7 +2011,7 @@
         <v>1001</v>
       </c>
       <c r="E29" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>15</v>
@@ -2033,8 +2033,8 @@
       <c r="D30" s="1">
         <v>1005</v>
       </c>
-      <c r="E30" s="1">
-        <v>5000</v>
+      <c r="E30" s="2">
+        <v>2000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>40</v>
@@ -2057,7 +2057,7 @@
         <v>1001</v>
       </c>
       <c r="E31" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>15</v>
@@ -2079,8 +2079,8 @@
       <c r="D32" s="1">
         <v>1004</v>
       </c>
-      <c r="E32" s="1">
-        <v>5000</v>
+      <c r="E32" s="2">
+        <v>2000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>42</v>
@@ -2103,7 +2103,7 @@
         <v>1001</v>
       </c>
       <c r="E33" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>15</v>
@@ -2125,8 +2125,8 @@
       <c r="D34" s="1">
         <v>1003</v>
       </c>
-      <c r="E34" s="1">
-        <v>5000</v>
+      <c r="E34" s="2">
+        <v>2000</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>44</v>
@@ -2149,7 +2149,7 @@
         <v>1001</v>
       </c>
       <c r="E35" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>15</v>
@@ -2171,8 +2171,8 @@
       <c r="D36" s="1">
         <v>1005</v>
       </c>
-      <c r="E36" s="1">
-        <v>5000</v>
+      <c r="E36" s="2">
+        <v>2000</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>46</v>
@@ -2195,7 +2195,7 @@
         <v>1001</v>
       </c>
       <c r="E37" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>15</v>
@@ -2217,8 +2217,8 @@
       <c r="D38" s="1">
         <v>1005</v>
       </c>
-      <c r="E38" s="1">
-        <v>5000</v>
+      <c r="E38" s="2">
+        <v>2000</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>48</v>
@@ -2241,7 +2241,7 @@
         <v>1001</v>
       </c>
       <c r="E39" s="2">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>15</v>
@@ -2263,8 +2263,8 @@
       <c r="D40" s="1">
         <v>1005</v>
       </c>
-      <c r="E40" s="1">
-        <v>5000</v>
+      <c r="E40" s="2">
+        <v>2000</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>50</v>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -1459,7 +1459,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1482,7 +1482,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -1505,7 +1505,7 @@
         <v>1001</v>
       </c>
       <c r="E7" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
@@ -1528,7 +1528,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1551,7 +1551,7 @@
         <v>1001</v>
       </c>
       <c r="E9" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -1574,7 +1574,7 @@
         <v>1003</v>
       </c>
       <c r="E10" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -1597,7 +1597,7 @@
         <v>1001</v>
       </c>
       <c r="E11" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>15</v>
@@ -1620,7 +1620,7 @@
         <v>1004</v>
       </c>
       <c r="E12" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1643,7 +1643,7 @@
         <v>1001</v>
       </c>
       <c r="E13" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>15</v>
@@ -1666,7 +1666,7 @@
         <v>1004</v>
       </c>
       <c r="E14" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
@@ -1689,7 +1689,7 @@
         <v>1001</v>
       </c>
       <c r="E15" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>15</v>
@@ -1712,7 +1712,7 @@
         <v>1004</v>
       </c>
       <c r="E16" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>26</v>
@@ -1735,7 +1735,7 @@
         <v>1001</v>
       </c>
       <c r="E17" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>15</v>
@@ -1758,7 +1758,7 @@
         <v>1003</v>
       </c>
       <c r="E18" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
@@ -1781,7 +1781,7 @@
         <v>1001</v>
       </c>
       <c r="E19" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
@@ -1804,7 +1804,7 @@
         <v>1003</v>
       </c>
       <c r="E20" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>30</v>
@@ -1827,7 +1827,7 @@
         <v>1001</v>
       </c>
       <c r="E21" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>15</v>
@@ -1850,7 +1850,7 @@
         <v>1003</v>
       </c>
       <c r="E22" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1873,7 +1873,7 @@
         <v>1001</v>
       </c>
       <c r="E23" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>15</v>
@@ -1896,7 +1896,7 @@
         <v>1003</v>
       </c>
       <c r="E24" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -1919,7 +1919,7 @@
         <v>1001</v>
       </c>
       <c r="E25" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>15</v>
@@ -1942,7 +1942,7 @@
         <v>1003</v>
       </c>
       <c r="E26" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>36</v>
@@ -1965,7 +1965,7 @@
         <v>1001</v>
       </c>
       <c r="E27" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>15</v>
@@ -1988,7 +1988,7 @@
         <v>1005</v>
       </c>
       <c r="E28" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -2011,7 +2011,7 @@
         <v>1001</v>
       </c>
       <c r="E29" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>15</v>
@@ -2034,7 +2034,7 @@
         <v>1005</v>
       </c>
       <c r="E30" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>40</v>
@@ -2057,7 +2057,7 @@
         <v>1001</v>
       </c>
       <c r="E31" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>15</v>
@@ -2080,7 +2080,7 @@
         <v>1004</v>
       </c>
       <c r="E32" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>42</v>
@@ -2103,7 +2103,7 @@
         <v>1001</v>
       </c>
       <c r="E33" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>15</v>
@@ -2126,7 +2126,7 @@
         <v>1003</v>
       </c>
       <c r="E34" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>44</v>
@@ -2149,7 +2149,7 @@
         <v>1001</v>
       </c>
       <c r="E35" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>15</v>
@@ -2172,7 +2172,7 @@
         <v>1005</v>
       </c>
       <c r="E36" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>46</v>
@@ -2195,7 +2195,7 @@
         <v>1001</v>
       </c>
       <c r="E37" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>15</v>
@@ -2218,7 +2218,7 @@
         <v>1005</v>
       </c>
       <c r="E38" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>48</v>
@@ -2241,7 +2241,7 @@
         <v>1001</v>
       </c>
       <c r="E39" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>15</v>
@@ -2264,7 +2264,7 @@
         <v>1005</v>
       </c>
       <c r="E40" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>50</v>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -1482,7 +1482,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -1528,7 +1528,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1574,7 +1574,7 @@
         <v>1003</v>
       </c>
       <c r="E10" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -1620,7 +1620,7 @@
         <v>1004</v>
       </c>
       <c r="E12" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1666,7 +1666,7 @@
         <v>1004</v>
       </c>
       <c r="E14" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
@@ -1712,7 +1712,7 @@
         <v>1004</v>
       </c>
       <c r="E16" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>26</v>
@@ -1758,7 +1758,7 @@
         <v>1003</v>
       </c>
       <c r="E18" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
@@ -1804,7 +1804,7 @@
         <v>1003</v>
       </c>
       <c r="E20" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>30</v>
@@ -1850,7 +1850,7 @@
         <v>1003</v>
       </c>
       <c r="E22" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1896,7 +1896,7 @@
         <v>1003</v>
       </c>
       <c r="E24" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -1942,7 +1942,7 @@
         <v>1003</v>
       </c>
       <c r="E26" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>36</v>
@@ -1988,7 +1988,7 @@
         <v>1005</v>
       </c>
       <c r="E28" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -2034,7 +2034,7 @@
         <v>1005</v>
       </c>
       <c r="E30" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>40</v>
@@ -2080,7 +2080,7 @@
         <v>1004</v>
       </c>
       <c r="E32" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>42</v>
@@ -2126,7 +2126,7 @@
         <v>1003</v>
       </c>
       <c r="E34" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>44</v>
@@ -2172,7 +2172,7 @@
         <v>1005</v>
       </c>
       <c r="E36" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>46</v>
@@ -2218,7 +2218,7 @@
         <v>1005</v>
       </c>
       <c r="E38" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>48</v>
@@ -2264,7 +2264,7 @@
         <v>1005</v>
       </c>
       <c r="E40" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>50</v>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -180,6 +185,18 @@
   </si>
   <si>
     <t>500_10000019_1</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>500_10000020_1</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>500_10000021_1</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1482,7 +1499,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -1528,7 +1545,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1574,7 +1591,7 @@
         <v>1003</v>
       </c>
       <c r="E10" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -1620,7 +1637,7 @@
         <v>1004</v>
       </c>
       <c r="E12" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1666,7 +1683,7 @@
         <v>1004</v>
       </c>
       <c r="E14" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
@@ -1712,7 +1729,7 @@
         <v>1004</v>
       </c>
       <c r="E16" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>26</v>
@@ -1758,7 +1775,7 @@
         <v>1003</v>
       </c>
       <c r="E18" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
@@ -1804,7 +1821,7 @@
         <v>1003</v>
       </c>
       <c r="E20" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>30</v>
@@ -1850,7 +1867,7 @@
         <v>1003</v>
       </c>
       <c r="E22" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1896,7 +1913,7 @@
         <v>1003</v>
       </c>
       <c r="E24" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -1942,7 +1959,7 @@
         <v>1003</v>
       </c>
       <c r="E26" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>36</v>
@@ -1988,7 +2005,7 @@
         <v>1005</v>
       </c>
       <c r="E28" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -2034,7 +2051,7 @@
         <v>1005</v>
       </c>
       <c r="E30" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>40</v>
@@ -2077,10 +2094,10 @@
         <v>41</v>
       </c>
       <c r="D32" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E32" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>42</v>
@@ -2126,7 +2143,7 @@
         <v>1003</v>
       </c>
       <c r="E34" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>44</v>
@@ -2172,7 +2189,7 @@
         <v>1005</v>
       </c>
       <c r="E36" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>46</v>
@@ -2218,7 +2235,7 @@
         <v>1005</v>
       </c>
       <c r="E38" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>48</v>
@@ -2264,12 +2281,104 @@
         <v>1005</v>
       </c>
       <c r="E40" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G40" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="3">
+        <v>10270001</v>
+      </c>
+      <c r="B41" s="3">
+        <v>102700</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E41" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="3">
+        <v>10270002</v>
+      </c>
+      <c r="B42" s="3">
+        <v>102700</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E42" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="3">
+        <v>10150001</v>
+      </c>
+      <c r="B43" s="3">
+        <v>101500</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E43" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="3">
+        <v>10150002</v>
+      </c>
+      <c r="B44" s="3">
+        <v>101500</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E44" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="1">
         <v>99999</v>
       </c>
     </row>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -1499,7 +1499,7 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
@@ -1545,7 +1545,7 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1591,7 +1591,7 @@
         <v>1003</v>
       </c>
       <c r="E10" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>20</v>
@@ -1637,7 +1637,7 @@
         <v>1004</v>
       </c>
       <c r="E12" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1683,7 +1683,7 @@
         <v>1004</v>
       </c>
       <c r="E14" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
@@ -1959,7 +1959,7 @@
         <v>1003</v>
       </c>
       <c r="E26" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>36</v>
@@ -2005,7 +2005,7 @@
         <v>1005</v>
       </c>
       <c r="E28" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -2051,7 +2051,7 @@
         <v>1005</v>
       </c>
       <c r="E30" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>40</v>
@@ -2097,7 +2097,7 @@
         <v>1005</v>
       </c>
       <c r="E32" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>42</v>
@@ -2143,7 +2143,7 @@
         <v>1003</v>
       </c>
       <c r="E34" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>44</v>
@@ -2189,7 +2189,7 @@
         <v>1005</v>
       </c>
       <c r="E36" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>46</v>
@@ -2235,7 +2235,7 @@
         <v>1005</v>
       </c>
       <c r="E38" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>48</v>
@@ -2281,7 +2281,7 @@
         <v>1005</v>
       </c>
       <c r="E40" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>50</v>
@@ -2327,7 +2327,7 @@
         <v>1003</v>
       </c>
       <c r="E42" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>52</v>
@@ -2373,7 +2373,7 @@
         <v>1005</v>
       </c>
       <c r="E44" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>54</v>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -1496,7 +1491,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="E6" s="2">
         <v>10000</v>
@@ -1542,7 +1537,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E8" s="2">
         <v>10000</v>
@@ -1588,7 +1583,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E10" s="2">
         <v>10000</v>
@@ -1634,7 +1629,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E12" s="2">
         <v>10000</v>
@@ -1680,7 +1675,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E14" s="2">
         <v>10000</v>
@@ -1726,7 +1721,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E16" s="2">
         <v>5000</v>
@@ -1772,7 +1767,7 @@
         <v>27</v>
       </c>
       <c r="D18" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E18" s="2">
         <v>5000</v>
@@ -1818,7 +1813,7 @@
         <v>29</v>
       </c>
       <c r="D20" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E20" s="2">
         <v>5000</v>
@@ -1864,7 +1859,7 @@
         <v>31</v>
       </c>
       <c r="D22" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E22" s="2">
         <v>5000</v>
@@ -1910,7 +1905,7 @@
         <v>33</v>
       </c>
       <c r="D24" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E24" s="2">
         <v>5000</v>
@@ -1956,7 +1951,7 @@
         <v>35</v>
       </c>
       <c r="D26" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E26" s="2">
         <v>10000</v>
@@ -2002,7 +1997,7 @@
         <v>37</v>
       </c>
       <c r="D28" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E28" s="2">
         <v>10000</v>
@@ -2048,7 +2043,7 @@
         <v>39</v>
       </c>
       <c r="D30" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E30" s="2">
         <v>10000</v>
@@ -2094,7 +2089,7 @@
         <v>41</v>
       </c>
       <c r="D32" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E32" s="2">
         <v>10000</v>
@@ -2140,7 +2135,7 @@
         <v>43</v>
       </c>
       <c r="D34" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E34" s="2">
         <v>10000</v>
@@ -2186,7 +2181,7 @@
         <v>45</v>
       </c>
       <c r="D36" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E36" s="2">
         <v>10000</v>
@@ -2232,7 +2227,7 @@
         <v>47</v>
       </c>
       <c r="D38" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E38" s="2">
         <v>10000</v>
@@ -2278,7 +2273,7 @@
         <v>49</v>
       </c>
       <c r="D40" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E40" s="2">
         <v>10000</v>
@@ -2324,7 +2319,7 @@
         <v>51</v>
       </c>
       <c r="D42" s="1">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E42" s="2">
         <v>10000</v>
@@ -2370,7 +2365,7 @@
         <v>53</v>
       </c>
       <c r="D44" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E44" s="2">
         <v>10000</v>

--- a/hall/resources/sample/dropItem.xlsx
+++ b/hall/resources/sample/dropItem.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -1372,7 +1377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -2241,30 +2246,30 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="3">
-        <v>10200001</v>
+        <v>10390003</v>
       </c>
       <c r="B39" s="3">
-        <v>102000</v>
+        <v>103900</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D39" s="1">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="E39" s="2">
-        <v>5000</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G39" s="1">
         <v>99999</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="3">
-        <v>10200002</v>
+        <v>10200001</v>
       </c>
       <c r="B40" s="3">
         <v>102000</v>
@@ -2273,44 +2278,44 @@
         <v>49</v>
       </c>
       <c r="D40" s="1">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E40" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2">
         <v>99999</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="3">
-        <v>10270001</v>
+        <v>10200002</v>
       </c>
       <c r="B41" s="3">
-        <v>102700</v>
+        <v>102000</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D41" s="1">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="E41" s="2">
-        <v>5000</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="2">
+        <v>10000</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="1">
         <v>99999</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="3">
-        <v>10270002</v>
+        <v>10270001</v>
       </c>
       <c r="B42" s="3">
         <v>102700</v>
@@ -2319,44 +2324,44 @@
         <v>51</v>
       </c>
       <c r="D42" s="1">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E42" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G42" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="2">
         <v>99999</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="3">
-        <v>10150001</v>
+        <v>10270002</v>
       </c>
       <c r="B43" s="3">
-        <v>101500</v>
+        <v>102700</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D43" s="1">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="E43" s="2">
-        <v>5000</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="2">
+        <v>10000</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="1">
         <v>99999</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="3">
-        <v>10150002</v>
+        <v>10150001</v>
       </c>
       <c r="B44" s="3">
         <v>101500</v>
@@ -2365,15 +2370,38 @@
         <v>53</v>
       </c>
       <c r="D44" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E44" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="2">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="3">
+        <v>10150002</v>
+      </c>
+      <c r="B45" s="3">
+        <v>101500</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="1">
         <v>1006</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E45" s="2">
         <v>10000</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G45" s="1">
         <v>99999</v>
       </c>
     </row>
